--- a/gdex_outputs/актуальное/aldan_actual.xlsx
+++ b/gdex_outputs/актуальное/aldan_actual.xlsx
@@ -12832,15 +12832,15 @@
         <v>680</v>
       </c>
       <c r="AG39" t="n">
-        <v>680</v>
+        <v>104.6</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>enriched</t>
+          <t>baro_below_station</t>
         </is>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>-575.4</v>
       </c>
       <c r="AJ39" t="n">
         <v>680</v>
